--- a/academias/Ciencias Sociales MCC - Estadisticos 20241.xlsx
+++ b/academias/Ciencias Sociales MCC - Estadisticos 20241.xlsx
@@ -1118,25 +1118,25 @@
         <v>37</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F2">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>21.6</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1153,25 +1153,25 @@
         <v>33</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>18.2</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1185,25 +1185,25 @@
         <v>70</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F4">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1287,25 +1287,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>22.5</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1322,25 +1322,25 @@
         <v>48</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F8">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J8">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1357,25 +1357,25 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F9">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>2.8</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J9">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1389,25 +1389,25 @@
         <v>124</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="F10">
-        <v>124</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>8.1</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1424,25 +1424,25 @@
         <v>40</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F11">
+        <v>16</v>
+      </c>
+      <c r="G11" s="1">
+        <v>60</v>
+      </c>
+      <c r="H11" s="1">
         <v>40</v>
       </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1">
-        <v>100</v>
-      </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J11">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1459,25 +1459,25 @@
         <v>34</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F12">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>38.2</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>61.8</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J12">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1529,25 +1529,25 @@
         <v>23</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F14">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>47.8</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>52.2</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="J14">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1564,25 +1564,25 @@
         <v>19</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F15">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>84.2</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>15.8</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J15">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1596,25 +1596,25 @@
         <v>149</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F16">
-        <v>149</v>
+        <v>85</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="J16">
-        <v>149</v>
+        <v>33</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="17" spans="2:11">
@@ -1625,25 +1625,25 @@
         <v>384</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="F17">
-        <v>384</v>
+        <v>150</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>60.9</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>39.1</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J17">
-        <v>384</v>
+        <v>74</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>19.3</v>
       </c>
     </row>
   </sheetData>
@@ -1711,19 +1711,19 @@
         <v>37</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1">
-        <v>83.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>16.2</v>
+        <v>21.6</v>
       </c>
       <c r="I2" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1746,16 +1746,16 @@
         <v>33</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>69.7</v>
+        <v>81.8</v>
       </c>
       <c r="H3" s="1">
-        <v>30.3</v>
+        <v>18.2</v>
       </c>
       <c r="I3" s="2">
         <v>7.4</v>
@@ -1778,19 +1778,19 @@
         <v>70</v>
       </c>
       <c r="E4">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1">
-        <v>77.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="H4" s="1">
-        <v>22.9</v>
+        <v>20</v>
       </c>
       <c r="I4" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1880,19 +1880,19 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1">
-        <v>80</v>
+        <v>77.5</v>
       </c>
       <c r="H7" s="1">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="I7" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1915,19 +1915,19 @@
         <v>48</v>
       </c>
       <c r="E8">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>97.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1962,7 +1962,7 @@
         <v>2.8</v>
       </c>
       <c r="I9" s="2">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1994,7 +1994,7 @@
         <v>8.1</v>
       </c>
       <c r="I10" s="2">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2017,19 +2017,19 @@
         <v>40</v>
       </c>
       <c r="E11">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F11">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G11" s="1">
-        <v>77.5</v>
+        <v>60</v>
       </c>
       <c r="H11" s="1">
-        <v>22.5</v>
+        <v>40</v>
       </c>
       <c r="I11" s="2">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2052,19 +2052,19 @@
         <v>34</v>
       </c>
       <c r="E12">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="G12" s="1">
-        <v>88.2</v>
+        <v>38.2</v>
       </c>
       <c r="H12" s="1">
-        <v>11.8</v>
+        <v>61.8</v>
       </c>
       <c r="I12" s="2">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2134,7 +2134,7 @@
         <v>52.2</v>
       </c>
       <c r="I14" s="2">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2157,19 +2157,19 @@
         <v>19</v>
       </c>
       <c r="E15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>78.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="H15" s="1">
-        <v>21.1</v>
+        <v>15.8</v>
       </c>
       <c r="I15" s="2">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2189,19 +2189,19 @@
         <v>149</v>
       </c>
       <c r="E16">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="F16">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="G16" s="1">
-        <v>76.5</v>
+        <v>61.1</v>
       </c>
       <c r="H16" s="1">
-        <v>23.5</v>
+        <v>38.9</v>
       </c>
       <c r="I16" s="2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2218,19 +2218,19 @@
         <v>384</v>
       </c>
       <c r="E17">
-        <v>282</v>
+        <v>261</v>
       </c>
       <c r="F17">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="G17" s="1">
-        <v>73.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="H17" s="1">
-        <v>26.6</v>
+        <v>32</v>
       </c>
       <c r="I17" s="2">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="J17">
         <v>41</v>

--- a/academias/Ciencias Sociales MCC - Estadisticos 20241.xlsx
+++ b/academias/Ciencias Sociales MCC - Estadisticos 20241.xlsx
@@ -627,25 +627,25 @@
         <v>41</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F5">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>87.8</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>12.2</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J5">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -659,25 +659,25 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>87.8</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>12.2</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J6">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1032,25 +1032,25 @@
         <v>384</v>
       </c>
       <c r="E17">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="F17">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="G17" s="1">
-        <v>73.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="H17" s="1">
-        <v>26.6</v>
+        <v>17.2</v>
       </c>
       <c r="I17" s="2">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>10.7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1220,25 +1220,25 @@
         <v>41</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F5">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J5">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1252,25 +1252,25 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J6">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1494,25 +1494,25 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F13">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>63.6</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>36.4</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J13">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1596,25 +1596,25 @@
         <v>149</v>
       </c>
       <c r="E16">
+        <v>85</v>
+      </c>
+      <c r="F16">
         <v>64</v>
       </c>
-      <c r="F16">
-        <v>85</v>
-      </c>
       <c r="G16" s="1">
+        <v>57</v>
+      </c>
+      <c r="H16" s="1">
         <v>43</v>
       </c>
-      <c r="H16" s="1">
-        <v>57</v>
-      </c>
       <c r="I16" s="2">
-        <v>4.9</v>
+        <v>6.3</v>
       </c>
       <c r="J16">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>22.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:11">
@@ -1625,25 +1625,25 @@
         <v>384</v>
       </c>
       <c r="E17">
-        <v>234</v>
+        <v>292</v>
       </c>
       <c r="F17">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c r="G17" s="1">
-        <v>60.9</v>
+        <v>76</v>
       </c>
       <c r="H17" s="1">
-        <v>39.1</v>
+        <v>24</v>
       </c>
       <c r="I17" s="2">
-        <v>5.7</v>
+        <v>7.1</v>
       </c>
       <c r="J17">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>19.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1813,25 +1813,25 @@
         <v>41</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F5">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J5">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1845,25 +1845,25 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J6">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2087,19 +2087,19 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1">
-        <v>81.8</v>
+        <v>63.6</v>
       </c>
       <c r="H13" s="1">
-        <v>18.2</v>
+        <v>36.4</v>
       </c>
       <c r="I13" s="2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2189,16 +2189,16 @@
         <v>149</v>
       </c>
       <c r="E16">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F16">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G16" s="1">
-        <v>61.1</v>
+        <v>57</v>
       </c>
       <c r="H16" s="1">
-        <v>38.9</v>
+        <v>43</v>
       </c>
       <c r="I16" s="2">
         <v>6.4</v>
@@ -2218,25 +2218,25 @@
         <v>384</v>
       </c>
       <c r="E17">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="F17">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="G17" s="1">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H17" s="1">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I17" s="2">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="J17">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>10.7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Ciencias Sociales MCC - Estadisticos 20241.xlsx
+++ b/academias/Ciencias Sociales MCC - Estadisticos 20241.xlsx
@@ -537,7 +537,7 @@
         <v>16.2</v>
       </c>
       <c r="I2" s="2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -572,7 +572,7 @@
         <v>30.3</v>
       </c>
       <c r="I3" s="2">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -604,7 +604,7 @@
         <v>22.9</v>
       </c>
       <c r="I4" s="2">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -639,7 +639,7 @@
         <v>12.2</v>
       </c>
       <c r="I5" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -671,7 +671,7 @@
         <v>12.2</v>
       </c>
       <c r="I6" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1044,7 +1044,7 @@
         <v>17.2</v>
       </c>
       <c r="I17" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1118,16 +1118,16 @@
         <v>37</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>78.40000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="H2" s="1">
-        <v>21.6</v>
+        <v>16.2</v>
       </c>
       <c r="I2" s="2">
         <v>7.4</v>
@@ -1153,16 +1153,16 @@
         <v>33</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>81.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>18.2</v>
+        <v>12.1</v>
       </c>
       <c r="I3" s="2">
         <v>7.3</v>
@@ -1185,16 +1185,16 @@
         <v>70</v>
       </c>
       <c r="E4">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
-        <v>80</v>
+        <v>85.7</v>
       </c>
       <c r="H4" s="1">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="I4" s="2">
         <v>7.4</v>
@@ -1625,16 +1625,16 @@
         <v>384</v>
       </c>
       <c r="E17">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F17">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G17" s="1">
-        <v>76</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>24</v>
+        <v>22.9</v>
       </c>
       <c r="I17" s="2">
         <v>7.1</v>
@@ -1711,19 +1711,19 @@
         <v>37</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>78.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>21.6</v>
+        <v>5.4</v>
       </c>
       <c r="I2" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1746,19 +1746,19 @@
         <v>33</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>81.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>18.2</v>
+        <v>12.1</v>
       </c>
       <c r="I3" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1778,19 +1778,19 @@
         <v>70</v>
       </c>
       <c r="E4">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>80</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>20</v>
+        <v>8.6</v>
       </c>
       <c r="I4" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I5" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1857,7 +1857,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I6" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1880,19 +1880,19 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>77.5</v>
+        <v>97.5</v>
       </c>
       <c r="H7" s="1">
-        <v>22.5</v>
+        <v>2.5</v>
       </c>
       <c r="I7" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1962,7 +1962,7 @@
         <v>2.8</v>
       </c>
       <c r="I9" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1982,19 +1982,19 @@
         <v>124</v>
       </c>
       <c r="E10">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>91.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>8.1</v>
+        <v>1.6</v>
       </c>
       <c r="I10" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2218,16 +2218,16 @@
         <v>384</v>
       </c>
       <c r="E17">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F17">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="G17" s="1">
-        <v>76</v>
+        <v>80.2</v>
       </c>
       <c r="H17" s="1">
-        <v>24</v>
+        <v>19.8</v>
       </c>
       <c r="I17" s="2">
         <v>7.1</v>

--- a/academias/Ciencias Sociales MCC - Estadisticos 20241.xlsx
+++ b/academias/Ciencias Sociales MCC - Estadisticos 20241.xlsx
@@ -1813,19 +1813,19 @@
         <v>41</v>
       </c>
       <c r="E5">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>90.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>9.800000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="I5" s="2">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1845,19 +1845,19 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>90.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>9.800000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="I6" s="2">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2017,16 +2017,16 @@
         <v>40</v>
       </c>
       <c r="E11">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F11">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1">
-        <v>60</v>
+        <v>72.5</v>
       </c>
       <c r="H11" s="1">
-        <v>40</v>
+        <v>27.5</v>
       </c>
       <c r="I11" s="2">
         <v>6.3</v>
@@ -2052,19 +2052,19 @@
         <v>34</v>
       </c>
       <c r="E12">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G12" s="1">
-        <v>38.2</v>
+        <v>52.9</v>
       </c>
       <c r="H12" s="1">
-        <v>61.8</v>
+        <v>47.1</v>
       </c>
       <c r="I12" s="2">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2087,19 +2087,19 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1">
-        <v>63.6</v>
+        <v>75.8</v>
       </c>
       <c r="H13" s="1">
-        <v>36.4</v>
+        <v>24.2</v>
       </c>
       <c r="I13" s="2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2134,7 +2134,7 @@
         <v>52.2</v>
       </c>
       <c r="I14" s="2">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2157,19 +2157,19 @@
         <v>19</v>
       </c>
       <c r="E15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>84.2</v>
+        <v>94.7</v>
       </c>
       <c r="H15" s="1">
-        <v>15.8</v>
+        <v>5.3</v>
       </c>
       <c r="I15" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2189,19 +2189,19 @@
         <v>149</v>
       </c>
       <c r="E16">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="F16">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="G16" s="1">
-        <v>57</v>
+        <v>67.8</v>
       </c>
       <c r="H16" s="1">
-        <v>43</v>
+        <v>32.2</v>
       </c>
       <c r="I16" s="2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2218,19 +2218,19 @@
         <v>384</v>
       </c>
       <c r="E17">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="F17">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="G17" s="1">
-        <v>80.2</v>
+        <v>85.2</v>
       </c>
       <c r="H17" s="1">
-        <v>19.8</v>
+        <v>14.8</v>
       </c>
       <c r="I17" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J17">
         <v>0</v>
